--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_DEER_BUCK_PREMIUM_LIMITED_ENTRY.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026_DEER_BUCK_PREMIUM_LIMITED_ENTRY.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -535,6 +535,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -598,10 +599,15 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Average Harvest Age Prior Year</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>Avg Days Hunted Prior Year</t>
         </is>
@@ -657,7 +663,8 @@
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -724,8 +731,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
@@ -792,8 +804,13 @@
           <t>67.6</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>12.1</t>
         </is>
@@ -861,7 +878,8 @@
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr"/>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -928,8 +946,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -996,8 +1019,13 @@
           <t>93.2</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr"/>
-      <c r="N9" s="6" t="inlineStr">
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
@@ -1064,8 +1092,13 @@
           <t>90</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr"/>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
@@ -1132,8 +1165,13 @@
           <t>70</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr"/>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -1200,8 +1238,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -1268,8 +1311,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr"/>
-      <c r="N13" s="6" t="inlineStr">
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" s="6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
